--- a/Comparativa_Nike_Adidas.xlsx
+++ b/Comparativa_Nike_Adidas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ncrespo\Desktop\Nike_Scrapper2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ncrespo\Desktop\Nike_Scrapper_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0251C177-DA96-4A88-98C6-13E399D00E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BF407A-3504-40AB-A65A-D2CA6184EC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="111">
   <si>
     <t>NIKE</t>
   </si>
@@ -228,9 +228,6 @@
     </r>
   </si>
   <si>
-    <t>EQ AGRAVIC</t>
-  </si>
-  <si>
     <t>Sportswear</t>
   </si>
   <si>
@@ -325,9 +322,6 @@
     </r>
   </si>
   <si>
-    <t>NIKE AIR MAX SC</t>
-  </si>
-  <si>
     <t>https://www.adidas.com.ar/search?q=RIVALRY+LOW</t>
   </si>
   <si>
@@ -396,18 +390,9 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">PREMIER </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPEEDPORTAL </t>
-  </si>
-  <si>
     <t>FUTBOL</t>
   </si>
   <si>
-    <t>https://www.adidas.com.ar/search?q=SPEEDPORTAL</t>
-  </si>
-  <si>
     <t>https://www.adidas.com/us/men-soccer-shoes</t>
   </si>
   <si>
@@ -432,306 +417,60 @@
     <t>PUMA</t>
   </si>
   <si>
-    <t>URL_PUMA_ARG</t>
-  </si>
-  <si>
-    <t>URL_PUMA_USA</t>
-  </si>
-  <si>
     <t>DEVIATE NITRO ELITE</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=DEVIATE+NITRO+ELITE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=DEVIATE+NITRO+ELITE</t>
-  </si>
-  <si>
     <t>FAST-R NITRO ELITE</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=FAST-R+NITRO+ELITE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=FAST-R+NITRO+ELITE</t>
-  </si>
-  <si>
     <t>MAGNIFY NITRO</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=MAGNIFY+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=MAGNIFY+NITRO</t>
-  </si>
-  <si>
     <t>DEVIATE NITRO</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=DEVIATE+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=DEVIATE+NITRO</t>
-  </si>
-  <si>
-    <t>MAGMAX NITRO</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=MAGMAX+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=MAGMAX+NITRO</t>
-  </si>
-  <si>
     <t>VELOCITY NITRO</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=VELOCITY+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=VELOCITY+NITRO</t>
-  </si>
-  <si>
     <t>FOREVERRUN NITRO</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=FOREVERRUN+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=FOREVERRUN+NITRO</t>
-  </si>
-  <si>
     <t>ELECTRIFY NITRO</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=ELECTRIFY+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=ELECTRIFY+NITRO</t>
-  </si>
-  <si>
     <t>SCORCH RUN</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=SCORCH+RUN</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=SCORCH+RUN</t>
-  </si>
-  <si>
     <t>TRANSPORT</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=TRANSPORT</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=TRANSPORT</t>
-  </si>
-  <si>
-    <t>ACCELERATE</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=ACCELERATE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=ACCELERATE</t>
-  </si>
-  <si>
-    <t>RETALIATE</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=RETALIATE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=RETALIATE</t>
-  </si>
-  <si>
-    <t>DIVIDE</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=DIVIDE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=DIVIDE</t>
-  </si>
-  <si>
-    <t>VOYAGE NITRO</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=VOYAGE+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=VOYAGE+NITRO</t>
-  </si>
-  <si>
-    <t>FAST-TRAC NITRO</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=FAST-TRAC+NITRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=FAST-TRAC+NITRO</t>
-  </si>
-  <si>
     <t>SUEDE XL</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=SUEDE+XL</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=SUEDE+XL</t>
-  </si>
-  <si>
     <t>CA PRO</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=CA+PRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=CA+PRO</t>
-  </si>
-  <si>
     <t>PALERMO</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=PALERMO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=PALERMO</t>
-  </si>
-  <si>
-    <t>SUPER TEAM</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=SUPER+TEAM</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=SUPER+TEAM</t>
-  </si>
-  <si>
-    <t>SLIPSTREAM</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=SLIPSTREAM</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=SLIPSTREAM</t>
-  </si>
-  <si>
-    <t>VELOPHASIS</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=VELOPHASIS</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=VELOPHASIS</t>
-  </si>
-  <si>
-    <t>MILENNIO</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=MILENNIO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=MILENNIO</t>
-  </si>
-  <si>
     <t>SHUFFLE</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=SHUFFLE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=SHUFFLE</t>
-  </si>
-  <si>
     <t>SMASH</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=SMASH</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=SMASH</t>
-  </si>
-  <si>
     <t>BARI</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=BARI</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=BARI</t>
-  </si>
-  <si>
-    <t>ULTRA</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=ULTRA</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=ULTRA</t>
-  </si>
-  <si>
-    <t>FUTURE</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=FUTURE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=FUTURE</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=KING</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=KING</t>
-  </si>
-  <si>
-    <t>ULTRA MATCH</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=ULTRA+MATCH</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=ULTRA+MATCH</t>
-  </si>
-  <si>
     <t>ULTIMATE</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=ULTIMATE</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=ULTIMATE</t>
-  </si>
-  <si>
-    <t>https://ar.puma.com/buscar?q=PRO</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=PRO</t>
-  </si>
-  <si>
     <t>MATCH</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=MATCH</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=MATCH</t>
-  </si>
-  <si>
     <t>PLAY</t>
   </si>
   <si>
-    <t>https://ar.puma.com/buscar?q=PLAY</t>
-  </si>
-  <si>
-    <t>https://us.puma.com/us/en/search?q=PLAY</t>
-  </si>
-  <si>
     <t>SAMBA "DECON"</t>
   </si>
   <si>
@@ -757,17 +496,33 @@
   </si>
   <si>
     <t>"ZOOM FLY"</t>
+  </si>
+  <si>
+    <t>EQUIPMENT AGRAVIC</t>
+  </si>
+  <si>
+    <t>SLIP STREAM</t>
+  </si>
+  <si>
+    <t>NIKE "AIR MAX SC"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -875,35 +630,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{7C8DFD73-4977-49CD-8327-3388E58251A6}"/>
@@ -1121,14 +877,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I997"/>
+  <dimension ref="A1:I996"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.5703125" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="24" width="8.7109375" customWidth="1"/>
+    <col min="5" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" customWidth="1"/>
+    <col min="11" max="24" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30">
@@ -1148,14 +909,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>87</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" ht="17.25" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -1174,18 +931,14 @@
         <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" spans="1:9" ht="25.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -1200,21 +953,17 @@
         <v>12</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>93</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9" ht="25.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -1226,14 +975,10 @@
         <v>14</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>96</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" ht="23.25" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -1252,14 +997,10 @@
         <v>18</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>99</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -1278,21 +1019,17 @@
         <v>22</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>102</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" ht="19.5" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
@@ -1304,14 +1041,10 @@
         <v>25</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>105</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -1330,14 +1063,10 @@
         <v>29</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>108</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" ht="16.5" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -1356,14 +1085,10 @@
         <v>33</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>96</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" ht="16.5" customHeight="1">
       <c r="A10" s="3" t="s">
@@ -1381,15 +1106,9 @@
       <c r="E10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>111</v>
-      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" ht="16.5" customHeight="1">
       <c r="A11" s="3" t="s">
@@ -1408,250 +1127,210 @@
         <v>41</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>114</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="12.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="G12" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>117</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" ht="11.25" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>120</v>
-      </c>
+      <c r="G13" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" ht="13.5" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>123</v>
-      </c>
+      <c r="G14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1">
       <c r="A15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>126</v>
-      </c>
+      <c r="G15" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>129</v>
-      </c>
+      <c r="G16" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" ht="12" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>132</v>
-      </c>
+      <c r="G17" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>129</v>
-      </c>
+      <c r="G18" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" ht="12" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>135</v>
-      </c>
+      <c r="G19" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="E20" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="19.5" customHeight="1">
+      <c r="G20" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" ht="33" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
@@ -1659,290 +1338,188 @@
         <v>75</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="C22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G21" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="33" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>153</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="8"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
       <c r="E26" s="8"/>
-      <c r="G26" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>156</v>
-      </c>
+      <c r="G26" s="9"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="E27" s="8"/>
-      <c r="G27" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>159</v>
-      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="E28" s="8"/>
-      <c r="G28" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>162</v>
-      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="G29" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>165</v>
-      </c>
+      <c r="G29" s="9"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="G30" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>168</v>
-      </c>
+      <c r="G30" s="9"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="G31" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>171</v>
-      </c>
+      <c r="D31" s="3"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
-      <c r="G32" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="G32" s="9"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="G33" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>177</v>
-      </c>
+      <c r="G33" s="9"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="G34" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>179</v>
-      </c>
+      <c r="G34" s="9"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="G35" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>182</v>
-      </c>
+      <c r="G35" s="9"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
-      <c r="G36" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
@@ -7703,12 +7280,6 @@
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
       <c r="D996" s="3"/>
-    </row>
-    <row r="997" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A997" s="3"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7750,86 +7321,14 @@
     <hyperlink ref="E19" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
     <hyperlink ref="D20" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
     <hyperlink ref="E20" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="D21" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="E21" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="D22" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="E22" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="D23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="E23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="D24" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="E24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D25" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="E25" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="H2" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="I2" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H3" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="I3" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H4" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="I4" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H5" r:id="rId55" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="I5" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H6" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="I6" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H7" r:id="rId59" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="I7" r:id="rId60" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="H8" r:id="rId61" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="I8" r:id="rId62" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H9" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="I9" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="H10" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="I10" r:id="rId66" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="H11" r:id="rId67" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="I11" r:id="rId68" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="H12" r:id="rId69" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="I12" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="H13" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="I13" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="H14" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="I14" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H15" r:id="rId75" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="I15" r:id="rId76" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="H16" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="I16" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="H17" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="I17" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="H18" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="I18" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H19" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="I19" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H20" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="I20" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="H21" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="I21" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="H22" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="I22" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="H23" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="I23" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="H24" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="I24" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="H25" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="I25" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="H26" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="I26" r:id="rId98" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="H27" r:id="rId99" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="I27" r:id="rId100" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="H28" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="I28" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="H29" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="I29" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="H30" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="I30" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="H31" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="I31" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="H32" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="I32" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="H33" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="I33" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="H34" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="I34" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="H35" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="I35" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="H36" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="I36" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D21" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E21" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="D22" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="E22" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="D23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="E23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D24" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="E24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
